--- a/examples/HFP_cameron.xlsx
+++ b/examples/HFP_cameron.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,60 +431,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -524,10 +534,17 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -565,10 +582,17 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -606,10 +630,17 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -647,10 +678,17 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -688,10 +726,17 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -729,10 +774,17 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -770,10 +822,17 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -811,10 +870,17 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -852,10 +918,17 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -893,10 +966,17 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -934,10 +1014,17 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -975,10 +1062,17 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1016,10 +1110,17 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1057,10 +1158,17 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1098,10 +1206,17 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1139,10 +1254,17 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1180,10 +1302,17 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1221,10 +1350,17 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1262,10 +1398,17 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1303,10 +1446,17 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1344,10 +1494,17 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1385,10 +1542,17 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1426,10 +1590,17 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1467,10 +1638,17 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1508,10 +1686,17 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1549,10 +1734,17 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,10 +1782,17 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1610,10 +1809,6 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/examples/HFP_cameron.xlsx
+++ b/examples/HFP_cameron.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,70 +431,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>HSA ctrb</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>HSA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>Roth conv fixed</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -534,17 +524,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -582,17 +565,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -630,17 +606,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -678,17 +647,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -726,17 +688,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -774,17 +729,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -822,17 +770,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -870,17 +811,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,17 +852,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -966,17 +893,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1014,17 +934,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1062,17 +975,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1110,17 +1016,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1158,17 +1057,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1206,17 +1098,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1254,17 +1139,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1302,17 +1180,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1350,17 +1221,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1398,17 +1262,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1446,17 +1303,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1494,17 +1344,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1542,17 +1385,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,17 +1426,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1638,17 +1467,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1686,17 +1508,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1734,17 +1549,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1782,17 +1590,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1809,6 +1610,10 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
